--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/7.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/7.xlsx
@@ -426,13 +426,13 @@
         <v>-7.089268233570683</v>
       </c>
       <c r="E2">
-        <v>-14.11725261565349</v>
+        <v>-14.77823321028706</v>
       </c>
       <c r="F2">
-        <v>-0.4200909365966238</v>
+        <v>-1.562499048736644</v>
       </c>
       <c r="G2">
-        <v>-12.47191547842316</v>
+        <v>-12.57647488463643</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-6.49492539013707</v>
       </c>
       <c r="E3">
-        <v>-14.95077259845331</v>
+        <v>-16.17660786995964</v>
       </c>
       <c r="F3">
-        <v>-0.4526979626730208</v>
+        <v>-1.647858167758119</v>
       </c>
       <c r="G3">
-        <v>-12.62058106483848</v>
+        <v>-11.56280710827717</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-5.916448562881739</v>
       </c>
       <c r="E4">
-        <v>-15.22401166312812</v>
+        <v>-16.80105726477333</v>
       </c>
       <c r="F4">
-        <v>-0.3611641930310782</v>
+        <v>-1.523395137120091</v>
       </c>
       <c r="G4">
-        <v>-11.73594404508283</v>
+        <v>-10.23696063153078</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-5.433368733701858</v>
       </c>
       <c r="E5">
-        <v>-16.27365759641802</v>
+        <v>-16.81217013998816</v>
       </c>
       <c r="F5">
-        <v>-0.4478859764301584</v>
+        <v>-1.454658866770594</v>
       </c>
       <c r="G5">
-        <v>-11.78640923266709</v>
+        <v>-10.77364051101512</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-5.03914052465633</v>
       </c>
       <c r="E6">
-        <v>-16.6103405819403</v>
+        <v>-17.8964996557028</v>
       </c>
       <c r="F6">
-        <v>-0.01914454629360713</v>
+        <v>-1.996288549825856</v>
       </c>
       <c r="G6">
-        <v>-11.59590807136885</v>
+        <v>-11.9850445422112</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-4.748886738586644</v>
       </c>
       <c r="E7">
-        <v>-17.46942832898743</v>
+        <v>-19.108088347981</v>
       </c>
       <c r="F7">
-        <v>-0.501173194717445</v>
+        <v>-1.298886033408952</v>
       </c>
       <c r="G7">
-        <v>-11.43432431567399</v>
+        <v>-10.27842870959905</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-4.554461750718221</v>
       </c>
       <c r="E8">
-        <v>-16.61558002636717</v>
+        <v>-19.19704569138768</v>
       </c>
       <c r="F8">
-        <v>-0.1590591140960548</v>
+        <v>-1.218902190464243</v>
       </c>
       <c r="G8">
-        <v>-11.32814726723192</v>
+        <v>-10.10674535394422</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-4.449414932615599</v>
       </c>
       <c r="E9">
-        <v>-18.95464100623109</v>
+        <v>-19.33803972961649</v>
       </c>
       <c r="F9">
-        <v>-0.2985661251363252</v>
+        <v>-1.529732147751507</v>
       </c>
       <c r="G9">
-        <v>-11.44220580985978</v>
+        <v>-10.33786803814839</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.415019614904773</v>
       </c>
       <c r="E10">
-        <v>-19.47881640109294</v>
+        <v>-20.22281750970913</v>
       </c>
       <c r="F10">
-        <v>0.002340819032803651</v>
+        <v>-0.9529059621186966</v>
       </c>
       <c r="G10">
-        <v>-11.77406855838202</v>
+        <v>-9.995758034696005</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.429534267007346</v>
       </c>
       <c r="E11">
-        <v>-19.25283649116217</v>
+        <v>-21.10733716678334</v>
       </c>
       <c r="F11">
-        <v>-0.006486264011427881</v>
+        <v>-1.41642474092698</v>
       </c>
       <c r="G11">
-        <v>-11.47389256645934</v>
+        <v>-9.747523780059334</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.468917003165371</v>
       </c>
       <c r="E12">
-        <v>-20.64095868568138</v>
+        <v>-21.35028074034684</v>
       </c>
       <c r="F12">
-        <v>0.3140181961731316</v>
+        <v>-0.8915438183889205</v>
       </c>
       <c r="G12">
-        <v>-11.26218158900085</v>
+        <v>-9.577405567088363</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.50590742502519</v>
       </c>
       <c r="E13">
-        <v>-20.16212237258433</v>
+        <v>-21.95636264458542</v>
       </c>
       <c r="F13">
-        <v>0.6227706080141746</v>
+        <v>-0.8856607530942384</v>
       </c>
       <c r="G13">
-        <v>-10.84798971033058</v>
+        <v>-11.03763119158025</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.521913850021733</v>
       </c>
       <c r="E14">
-        <v>-21.64035667138217</v>
+        <v>-21.72999328589</v>
       </c>
       <c r="F14">
-        <v>0.421348103819058</v>
+        <v>-0.8204210215519577</v>
       </c>
       <c r="G14">
-        <v>-10.53730724697456</v>
+        <v>-8.267187548629611</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.499516358890279</v>
       </c>
       <c r="E15">
-        <v>-22.43790698513907</v>
+        <v>-21.95888500460769</v>
       </c>
       <c r="F15">
-        <v>1.184687008763997</v>
+        <v>-0.5039449120472121</v>
       </c>
       <c r="G15">
-        <v>-10.71783021351053</v>
+        <v>-9.967444373859555</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.435453294826597</v>
       </c>
       <c r="E16">
-        <v>-22.62698888885533</v>
+        <v>-23.37558639858931</v>
       </c>
       <c r="F16">
-        <v>1.361629599471582</v>
+        <v>-0.1784130900950625</v>
       </c>
       <c r="G16">
-        <v>-10.51049966683389</v>
+        <v>-9.96517704976198</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.330425015469381</v>
       </c>
       <c r="E17">
-        <v>-22.94507343162811</v>
+        <v>-23.63020437814459</v>
       </c>
       <c r="F17">
-        <v>1.547029821361751</v>
+        <v>1.458707632140462</v>
       </c>
       <c r="G17">
-        <v>-9.97888599343734</v>
+        <v>-9.275264123451574</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.196389720615776</v>
       </c>
       <c r="E18">
-        <v>-24.85133456515694</v>
+        <v>-25.55963771317067</v>
       </c>
       <c r="F18">
-        <v>2.125072878709274</v>
+        <v>0.4892195586000327</v>
       </c>
       <c r="G18">
-        <v>-9.401020220938852</v>
+        <v>-8.547479337902057</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.04506364513634</v>
       </c>
       <c r="E19">
-        <v>-24.78968392001652</v>
+        <v>-25.34822590412258</v>
       </c>
       <c r="F19">
-        <v>2.172710631309468</v>
+        <v>1.105006348288712</v>
       </c>
       <c r="G19">
-        <v>-9.647275898975177</v>
+        <v>-9.261988301022061</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.893018583902971</v>
       </c>
       <c r="E20">
-        <v>-25.81995251302759</v>
+        <v>-26.89246724005623</v>
       </c>
       <c r="F20">
-        <v>2.480473972471568</v>
+        <v>1.67607952230908</v>
       </c>
       <c r="G20">
-        <v>-8.578112822381033</v>
+        <v>-8.844715355307477</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.750874724613977</v>
       </c>
       <c r="E21">
-        <v>-26.12873104171461</v>
+        <v>-27.28960988205491</v>
       </c>
       <c r="F21">
-        <v>2.804928916800079</v>
+        <v>1.761214153764397</v>
       </c>
       <c r="G21">
-        <v>-9.36013948152973</v>
+        <v>-8.048307102063733</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-3.629346034090485</v>
       </c>
       <c r="E22">
-        <v>-26.97575946247931</v>
+        <v>-25.8118103167618</v>
       </c>
       <c r="F22">
-        <v>3.128868616604048</v>
+        <v>1.753697547951394</v>
       </c>
       <c r="G22">
-        <v>-9.016346211417352</v>
+        <v>-8.186528560255342</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-3.531229485395595</v>
       </c>
       <c r="E23">
-        <v>-27.7371182119669</v>
+        <v>-28.04911195719936</v>
       </c>
       <c r="F23">
-        <v>3.433921539624188</v>
+        <v>2.096058482058818</v>
       </c>
       <c r="G23">
-        <v>-8.252474551157063</v>
+        <v>-9.260478939104717</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-3.45744715416382</v>
       </c>
       <c r="E24">
-        <v>-28.15109319185209</v>
+        <v>-29.00248253308618</v>
       </c>
       <c r="F24">
-        <v>3.666411134893897</v>
+        <v>2.534997114923832</v>
       </c>
       <c r="G24">
-        <v>-8.603004169130982</v>
+        <v>-7.414923060779441</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-3.400896939094186</v>
       </c>
       <c r="E25">
-        <v>-27.80529891662639</v>
+        <v>-28.63710713625131</v>
       </c>
       <c r="F25">
-        <v>3.483404894797819</v>
+        <v>2.324623272574064</v>
       </c>
       <c r="G25">
-        <v>-8.05565375713533</v>
+        <v>-7.842482636082885</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-3.35117139339454</v>
       </c>
       <c r="E26">
-        <v>-27.73262596575129</v>
+        <v>-29.21370867469996</v>
       </c>
       <c r="F26">
-        <v>3.418152737744497</v>
+        <v>2.73757104980884</v>
       </c>
       <c r="G26">
-        <v>-8.568367594349482</v>
+        <v>-8.588005705382759</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.292745675991365</v>
       </c>
       <c r="E27">
-        <v>-28.38594438236389</v>
+        <v>-29.13570118144383</v>
       </c>
       <c r="F27">
-        <v>3.312076978346409</v>
+        <v>2.824402177705089</v>
       </c>
       <c r="G27">
-        <v>-9.148339911089133</v>
+        <v>-8.242299483101224</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.207946018886008</v>
       </c>
       <c r="E28">
-        <v>-28.08649903860669</v>
+        <v>-28.90017524830489</v>
       </c>
       <c r="F28">
-        <v>3.17197851298054</v>
+        <v>2.430185444182416</v>
       </c>
       <c r="G28">
-        <v>-8.859631788516712</v>
+        <v>-8.505020330922843</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.082201234356154</v>
       </c>
       <c r="E29">
-        <v>-28.80582449235508</v>
+        <v>-28.6761244683014</v>
       </c>
       <c r="F29">
-        <v>3.126554158080626</v>
+        <v>2.730811571801996</v>
       </c>
       <c r="G29">
-        <v>-8.856419472610016</v>
+        <v>-9.68703774183253</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-2.902494353964622</v>
       </c>
       <c r="E30">
-        <v>-27.5591763543095</v>
+        <v>-28.06795493754527</v>
       </c>
       <c r="F30">
-        <v>3.079499576132003</v>
+        <v>2.450772030876789</v>
       </c>
       <c r="G30">
-        <v>-9.851220225002464</v>
+        <v>-9.307656342686412</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.666187907925344</v>
       </c>
       <c r="E31">
-        <v>-28.19211210941357</v>
+        <v>-29.15650499103507</v>
       </c>
       <c r="F31">
-        <v>2.903029154844013</v>
+        <v>2.339951382995466</v>
       </c>
       <c r="G31">
-        <v>-9.261381275033564</v>
+        <v>-9.513100186966366</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-2.373139013751547</v>
       </c>
       <c r="E32">
-        <v>-28.27182230889659</v>
+        <v>-28.31529113089621</v>
       </c>
       <c r="F32">
-        <v>2.861171749980554</v>
+        <v>2.045125483930288</v>
       </c>
       <c r="G32">
-        <v>-10.34435501317141</v>
+        <v>-8.807335679302282</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-2.035941137260584</v>
       </c>
       <c r="E33">
-        <v>-28.11840666646473</v>
+        <v>-29.01334181375658</v>
       </c>
       <c r="F33">
-        <v>2.813606893711806</v>
+        <v>1.631031246210038</v>
       </c>
       <c r="G33">
-        <v>-9.578928053891945</v>
+        <v>-9.340688400125343</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-1.66748219083984</v>
       </c>
       <c r="E34">
-        <v>-26.9517268509206</v>
+        <v>-27.24559764317436</v>
       </c>
       <c r="F34">
-        <v>2.673783446323666</v>
+        <v>1.987814056800201</v>
       </c>
       <c r="G34">
-        <v>-10.13232903844321</v>
+        <v>-9.50089404276523</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.291701376474389</v>
       </c>
       <c r="E35">
-        <v>-26.92911165172629</v>
+        <v>-28.81574637890589</v>
       </c>
       <c r="F35">
-        <v>2.661488817331316</v>
+        <v>1.333617527378514</v>
       </c>
       <c r="G35">
-        <v>-9.573438570222994</v>
+        <v>-8.843068182084634</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.9294831430928109</v>
       </c>
       <c r="E36">
-        <v>-26.56848662412547</v>
+        <v>-27.17209598155586</v>
       </c>
       <c r="F36">
-        <v>2.524394012167998</v>
+        <v>1.871645468966404</v>
       </c>
       <c r="G36">
-        <v>-8.897621771731963</v>
+        <v>-8.296114797897676</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.6054681989635023</v>
       </c>
       <c r="E37">
-        <v>-27.14908680512289</v>
+        <v>-26.12220551066955</v>
       </c>
       <c r="F37">
-        <v>2.255270696876884</v>
+        <v>1.839410379853864</v>
       </c>
       <c r="G37">
-        <v>-8.972374561299231</v>
+        <v>-8.378903299064026</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.3352431647993158</v>
       </c>
       <c r="E38">
-        <v>-26.60192940467211</v>
+        <v>-26.49407473923143</v>
       </c>
       <c r="F38">
-        <v>2.606616103835071</v>
+        <v>1.414194481383628</v>
       </c>
       <c r="G38">
-        <v>-9.269364487087692</v>
+        <v>-8.646424574027114</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.1320979251994527</v>
       </c>
       <c r="E39">
-        <v>-25.85719921174069</v>
+        <v>-26.72529862206308</v>
       </c>
       <c r="F39">
-        <v>2.435743789455201</v>
+        <v>1.385368952501011</v>
       </c>
       <c r="G39">
-        <v>-8.805504757672113</v>
+        <v>-8.099635250918126</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.0005312848241970265</v>
       </c>
       <c r="E40">
-        <v>-25.95799398620341</v>
+        <v>-26.63419478197676</v>
       </c>
       <c r="F40">
-        <v>2.09490208116451</v>
+        <v>1.47237735102146</v>
       </c>
       <c r="G40">
-        <v>-8.375864887899979</v>
+        <v>-8.690140288863596</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.06250187625822244</v>
       </c>
       <c r="E41">
-        <v>-26.33820919236142</v>
+        <v>-25.49096793331836</v>
       </c>
       <c r="F41">
-        <v>2.139844326235995</v>
+        <v>1.246118735355608</v>
       </c>
       <c r="G41">
-        <v>-7.850774282963601</v>
+        <v>-8.878784278759191</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>0.06116120532013729</v>
       </c>
       <c r="E42">
-        <v>-25.29089995165948</v>
+        <v>-26.44733635899826</v>
       </c>
       <c r="F42">
-        <v>2.182516844623808</v>
+        <v>1.385413684340762</v>
       </c>
       <c r="G42">
-        <v>-8.040494513530696</v>
+        <v>-8.214153164564307</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>0.004843770421044972</v>
       </c>
       <c r="E43">
-        <v>-24.79201608413047</v>
+        <v>-24.21941318823059</v>
       </c>
       <c r="F43">
-        <v>1.892995810406159</v>
+        <v>1.310930200950641</v>
       </c>
       <c r="G43">
-        <v>-7.382616153305149</v>
+        <v>-8.370883993572743</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.094902445483994</v>
       </c>
       <c r="E44">
-        <v>-24.89801407522801</v>
+        <v>-24.91817936998417</v>
       </c>
       <c r="F44">
-        <v>1.82093613003663</v>
+        <v>1.217344565251965</v>
       </c>
       <c r="G44">
-        <v>-7.267858710485129</v>
+        <v>-5.790373860590566</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.228080875547038</v>
       </c>
       <c r="E45">
-        <v>-24.38854263546907</v>
+        <v>-25.05778769516663</v>
       </c>
       <c r="F45">
-        <v>1.590094985898492</v>
+        <v>1.000348753884217</v>
       </c>
       <c r="G45">
-        <v>-8.045321190444639</v>
+        <v>-6.679637402745034</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.3841682072227959</v>
       </c>
       <c r="E46">
-        <v>-24.31892187607514</v>
+        <v>-24.99716048515194</v>
       </c>
       <c r="F46">
-        <v>1.550134542387444</v>
+        <v>0.86905086380569</v>
       </c>
       <c r="G46">
-        <v>-7.334546257459284</v>
+        <v>-6.998959322467075</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.5560809708768973</v>
       </c>
       <c r="E47">
-        <v>-24.08299743722353</v>
+        <v>-24.61265681410867</v>
       </c>
       <c r="F47">
-        <v>1.252407700677662</v>
+        <v>0.5782060984783668</v>
       </c>
       <c r="G47">
-        <v>-7.376637767623841</v>
+        <v>-6.481733805608686</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.7366218601969455</v>
       </c>
       <c r="E48">
-        <v>-24.00219587550467</v>
+        <v>-23.19844155235726</v>
       </c>
       <c r="F48">
-        <v>1.203144691233175</v>
+        <v>0.6207576752253717</v>
       </c>
       <c r="G48">
-        <v>-7.478460635056528</v>
+        <v>-6.680221460182616</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.9229302284758945</v>
       </c>
       <c r="E49">
-        <v>-24.00215964771261</v>
+        <v>-23.31225116111803</v>
       </c>
       <c r="F49">
-        <v>1.284039738320964</v>
+        <v>0.3047918400407507</v>
       </c>
       <c r="G49">
-        <v>-6.975154060053304</v>
+        <v>-7.335894839520216</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-1.111120490970821</v>
       </c>
       <c r="E50">
-        <v>-22.34090707189477</v>
+        <v>-23.03266317588447</v>
       </c>
       <c r="F50">
-        <v>1.185687676586579</v>
+        <v>0.4107549414720579</v>
       </c>
       <c r="G50">
-        <v>-7.439519097589039</v>
+        <v>-7.047636244301438</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-1.301674300307913</v>
       </c>
       <c r="E51">
-        <v>-23.01699012734392</v>
+        <v>-22.00919635083291</v>
       </c>
       <c r="F51">
-        <v>1.060723483669856</v>
+        <v>0.5330567615561825</v>
       </c>
       <c r="G51">
-        <v>-7.420944102341022</v>
+        <v>-6.737715024347206</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-1.491164718612863</v>
       </c>
       <c r="E52">
-        <v>-22.06795782955644</v>
+        <v>-23.6719523800213</v>
       </c>
       <c r="F52">
-        <v>1.162831363208535</v>
+        <v>0.2725782884806836</v>
       </c>
       <c r="G52">
-        <v>-7.463097955715209</v>
+        <v>-7.136006103340403</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-1.679837039098207</v>
       </c>
       <c r="E53">
-        <v>-21.68661956184453</v>
+        <v>-22.92432849219897</v>
       </c>
       <c r="F53">
-        <v>0.7720838323687854</v>
+        <v>0.2191510761023238</v>
       </c>
       <c r="G53">
-        <v>-7.203215364542509</v>
+        <v>-6.038132338101117</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-1.862222683519394</v>
       </c>
       <c r="E54">
-        <v>-21.57871055471575</v>
+        <v>-21.21566279352082</v>
       </c>
       <c r="F54">
-        <v>0.6521312622390002</v>
+        <v>-0.2941592105534318</v>
       </c>
       <c r="G54">
-        <v>-7.216576498732568</v>
+        <v>-6.842763332572829</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.036261148739472</v>
       </c>
       <c r="E55">
-        <v>-21.31471410549059</v>
+        <v>-23.44886616498144</v>
       </c>
       <c r="F55">
-        <v>0.2886834075259115</v>
+        <v>0.08393997841297175</v>
       </c>
       <c r="G55">
-        <v>-7.609197626871044</v>
+        <v>-6.621395720064891</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.196270881632669</v>
       </c>
       <c r="E56">
-        <v>-21.23827799271513</v>
+        <v>-21.60932303900761</v>
       </c>
       <c r="F56">
-        <v>0.3667934834054881</v>
+        <v>-0.09496667140665148</v>
       </c>
       <c r="G56">
-        <v>-7.32328182384571</v>
+        <v>-5.543986933691862</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.339174356767112</v>
       </c>
       <c r="E57">
-        <v>-21.02501856627191</v>
+        <v>-22.50507331162083</v>
       </c>
       <c r="F57">
-        <v>0.3447034098750337</v>
+        <v>0.01484005477364539</v>
       </c>
       <c r="G57">
-        <v>-7.397637585604286</v>
+        <v>-6.876927411449767</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-2.460068608465316</v>
       </c>
       <c r="E58">
-        <v>-20.32665089023101</v>
+        <v>-22.70901766703027</v>
       </c>
       <c r="F58">
-        <v>0.4758422534122235</v>
+        <v>-0.7563940198873755</v>
       </c>
       <c r="G58">
-        <v>-7.013924973999702</v>
+        <v>-6.315441496976027</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-2.554866256367507</v>
       </c>
       <c r="E59">
-        <v>-20.17383300636816</v>
+        <v>-19.43434225786361</v>
       </c>
       <c r="F59">
-        <v>0.4435259842942091</v>
+        <v>0.4767070689807462</v>
       </c>
       <c r="G59">
-        <v>-7.512178467801383</v>
+        <v>-6.27276264815233</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-2.620060002364407</v>
       </c>
       <c r="E60">
-        <v>-20.13227067192576</v>
+        <v>-22.0132629204918</v>
       </c>
       <c r="F60">
-        <v>-0.1295443835343084</v>
+        <v>-0.288105501573773</v>
       </c>
       <c r="G60">
-        <v>-6.970429101007704</v>
+        <v>-6.374073645021745</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-2.652462642308461</v>
       </c>
       <c r="E61">
-        <v>-19.27843595472753</v>
+        <v>-21.17182263665256</v>
       </c>
       <c r="F61">
-        <v>-0.08019273877772229</v>
+        <v>0.1063845931918244</v>
       </c>
       <c r="G61">
-        <v>-7.708408641942414</v>
+        <v>-6.716770987133271</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-2.651276554360452</v>
       </c>
       <c r="E62">
-        <v>-19.98686137153947</v>
+        <v>-20.39467762677423</v>
       </c>
       <c r="F62">
-        <v>0.1169048592073781</v>
+        <v>-0.415380011176903</v>
       </c>
       <c r="G62">
-        <v>-7.691664568324568</v>
+        <v>-7.343169307717504</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-2.615877290787537</v>
       </c>
       <c r="E63">
-        <v>-19.46583326611295</v>
+        <v>-19.58095613233595</v>
       </c>
       <c r="F63">
-        <v>-0.2851730809678628</v>
+        <v>-0.8548985012238759</v>
       </c>
       <c r="G63">
-        <v>-7.96134488707377</v>
+        <v>-7.035220101920499</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-2.547640164092717</v>
       </c>
       <c r="E64">
-        <v>-19.53712050394169</v>
+        <v>-18.71903808903402</v>
       </c>
       <c r="F64">
-        <v>-0.2420565576521485</v>
+        <v>-0.4247016295606059</v>
       </c>
       <c r="G64">
-        <v>-7.787239989908073</v>
+        <v>-6.764890101302527</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.447322749174589</v>
       </c>
       <c r="E65">
-        <v>-19.32755178381473</v>
+        <v>-18.9415446594009</v>
       </c>
       <c r="F65">
-        <v>-0.3783975484789191</v>
+        <v>-0.2183834740149442</v>
       </c>
       <c r="G65">
-        <v>-7.513159553047656</v>
+        <v>-7.882372446581054</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.316497013443525</v>
       </c>
       <c r="E66">
-        <v>-19.53928511451736</v>
+        <v>-20.17225709741349</v>
       </c>
       <c r="F66">
-        <v>-0.4010567104150968</v>
+        <v>-0.7321965796841992</v>
       </c>
       <c r="G66">
-        <v>-7.941204749141898</v>
+        <v>-7.943170200856006</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.156848141951204</v>
       </c>
       <c r="E67">
-        <v>-18.82803392992464</v>
+        <v>-20.35834567981069</v>
       </c>
       <c r="F67">
-        <v>-0.5373587679739359</v>
+        <v>-1.001985902367164</v>
       </c>
       <c r="G67">
-        <v>-8.712967747252652</v>
+        <v>-8.828483152252904</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-1.970192638900102</v>
       </c>
       <c r="E68">
-        <v>-18.72141553788805</v>
+        <v>-20.15640743838665</v>
       </c>
       <c r="F68">
-        <v>-0.5739900028931327</v>
+        <v>-0.423858351544556</v>
       </c>
       <c r="G68">
-        <v>-8.607745534284378</v>
+        <v>-7.166291778334077</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-1.76015145705381</v>
       </c>
       <c r="E69">
-        <v>-18.12073610314062</v>
+        <v>-19.76008897865736</v>
       </c>
       <c r="F69">
-        <v>-0.6634453987214514</v>
+        <v>-0.3627173819113273</v>
       </c>
       <c r="G69">
-        <v>-8.088429879292622</v>
+        <v>-8.439582929362837</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-1.528936127300277</v>
       </c>
       <c r="E70">
-        <v>-19.01410892689982</v>
+        <v>-19.20323611535616</v>
       </c>
       <c r="F70">
-        <v>-0.6346786839244329</v>
+        <v>-1.02813000596692</v>
       </c>
       <c r="G70">
-        <v>-7.880387307537591</v>
+        <v>-8.632328446207739</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-1.282842218851968</v>
       </c>
       <c r="E71">
-        <v>-18.74803390810514</v>
+        <v>-19.44123006682927</v>
       </c>
       <c r="F71">
-        <v>-0.8439764770179644</v>
+        <v>-0.7549534889739071</v>
       </c>
       <c r="G71">
-        <v>-8.494510578267942</v>
+        <v>-8.300603508990998</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.024636651451958</v>
       </c>
       <c r="E72">
-        <v>-19.21408633907854</v>
+        <v>-19.58673446516973</v>
       </c>
       <c r="F72">
-        <v>-1.025611769062409</v>
+        <v>-0.5958647008988593</v>
       </c>
       <c r="G72">
-        <v>-8.136719616982971</v>
+        <v>-8.31624181094331</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-0.7626404476289531</v>
       </c>
       <c r="E73">
-        <v>-18.85205295606132</v>
+        <v>-19.96212684650957</v>
       </c>
       <c r="F73">
-        <v>-1.143061841268337</v>
+        <v>-1.193385160988407</v>
       </c>
       <c r="G73">
-        <v>-8.422064487456963</v>
+        <v>-7.6113533894356</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-0.499376154637862</v>
       </c>
       <c r="E74">
-        <v>-19.16941747146688</v>
+        <v>-18.61006036203943</v>
       </c>
       <c r="F74">
-        <v>-0.892987662772</v>
+        <v>-0.648672294459925</v>
       </c>
       <c r="G74">
-        <v>-7.762991762583777</v>
+        <v>-7.527436148052801</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-0.2433363877365367</v>
       </c>
       <c r="E75">
-        <v>-18.59176079857444</v>
+        <v>-20.07659761247546</v>
       </c>
       <c r="F75">
-        <v>-1.171440051753443</v>
+        <v>-0.8495223967797071</v>
       </c>
       <c r="G75">
-        <v>-7.935288706670219</v>
+        <v>-7.961354730738448</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>0.003185792231472615</v>
       </c>
       <c r="E76">
-        <v>-18.9342809870926</v>
+        <v>-19.40617967800991</v>
       </c>
       <c r="F76">
-        <v>-1.168829866067221</v>
+        <v>-1.616198793990525</v>
       </c>
       <c r="G76">
-        <v>-7.535107644058782</v>
+        <v>-8.194288649243429</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>0.2328789398778215</v>
       </c>
       <c r="E77">
-        <v>-18.66359598175811</v>
+        <v>-20.64658757887292</v>
       </c>
       <c r="F77">
-        <v>-1.234356212730871</v>
+        <v>-1.114332403004445</v>
       </c>
       <c r="G77">
-        <v>-7.530579558306749</v>
+        <v>-6.481979897225644</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>0.4429252116957154</v>
       </c>
       <c r="E78">
-        <v>-19.34986810372452</v>
+        <v>-20.7618779986342</v>
       </c>
       <c r="F78">
-        <v>-1.327590620650761</v>
+        <v>-1.638895232459829</v>
       </c>
       <c r="G78">
-        <v>-7.771552469632368</v>
+        <v>-8.748316347112549</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>0.6272109091311994</v>
       </c>
       <c r="E79">
-        <v>-19.75146223567275</v>
+        <v>-21.53194047516453</v>
       </c>
       <c r="F79">
-        <v>-1.314171068725409</v>
+        <v>-1.499542297756479</v>
       </c>
       <c r="G79">
-        <v>-7.107052604299862</v>
+        <v>-8.084095385612597</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>0.782912734460448</v>
       </c>
       <c r="E80">
-        <v>-20.59396218242978</v>
+        <v>-20.9983322689447</v>
       </c>
       <c r="F80">
-        <v>-1.368633740357268</v>
+        <v>-1.704625357504567</v>
       </c>
       <c r="G80">
-        <v>-6.757943755261183</v>
+        <v>-8.166808418683079</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>0.9057585967007269</v>
       </c>
       <c r="E81">
-        <v>-21.20599450151444</v>
+        <v>-21.20740738540484</v>
       </c>
       <c r="F81">
-        <v>-1.586535785663678</v>
+        <v>-1.648521690047762</v>
       </c>
       <c r="G81">
-        <v>-6.941393571428177</v>
+        <v>-7.242297994537055</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>0.9938516589502917</v>
       </c>
       <c r="E82">
-        <v>-21.23801534122268</v>
+        <v>-21.99706909744037</v>
       </c>
       <c r="F82">
-        <v>-1.457532473290905</v>
+        <v>-2.055226890535041</v>
       </c>
       <c r="G82">
-        <v>-6.94380198805281</v>
+        <v>-6.723976549677811</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>1.045794254579246</v>
       </c>
       <c r="E83">
-        <v>-21.39571039159178</v>
+        <v>-23.95854591454473</v>
       </c>
       <c r="F83">
-        <v>-1.507192270721333</v>
+        <v>-1.584856684938203</v>
       </c>
       <c r="G83">
-        <v>-6.647379713594133</v>
+        <v>-6.736829094526156</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>1.062230504330012</v>
       </c>
       <c r="E84">
-        <v>-22.93446321702814</v>
+        <v>-24.71892651364667</v>
       </c>
       <c r="F84">
-        <v>-1.629066653225613</v>
+        <v>-1.457071072647546</v>
       </c>
       <c r="G84">
-        <v>-6.645286294239208</v>
+        <v>-7.583197227234004</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>1.045110282165489</v>
       </c>
       <c r="E85">
-        <v>-24.40953211249462</v>
+        <v>-24.64197415483433</v>
       </c>
       <c r="F85">
-        <v>-1.548476445342054</v>
+        <v>-1.531721886253032</v>
       </c>
       <c r="G85">
-        <v>-7.064130945080766</v>
+        <v>-6.682383785190289</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>0.9974879516029248</v>
       </c>
       <c r="E86">
-        <v>-24.31173065935096</v>
+        <v>-26.25440978084948</v>
       </c>
       <c r="F86">
-        <v>-1.820832878606296</v>
+        <v>-1.699745445134675</v>
       </c>
       <c r="G86">
-        <v>-7.076497869138313</v>
+        <v>-7.323258855294794</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>0.9236135529541885</v>
       </c>
       <c r="E87">
-        <v>-25.71405414835822</v>
+        <v>-28.2440808771256</v>
       </c>
       <c r="F87">
-        <v>-1.866049313288106</v>
+        <v>-1.858783702798152</v>
       </c>
       <c r="G87">
-        <v>-6.47840336572585</v>
+        <v>-7.654754107002375</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>0.828654028210328</v>
       </c>
       <c r="E88">
-        <v>-26.05945897481927</v>
+        <v>-28.83996918637292</v>
       </c>
       <c r="F88">
-        <v>-1.854913570292273</v>
+        <v>-1.628522415841973</v>
       </c>
       <c r="G88">
-        <v>-6.777099526725221</v>
+        <v>-7.704421957747689</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>0.7184558915820004</v>
       </c>
       <c r="E89">
-        <v>-27.96905759369176</v>
+        <v>-29.4779904177876</v>
       </c>
       <c r="F89">
-        <v>-1.492950978332404</v>
+        <v>-2.043451647904246</v>
       </c>
       <c r="G89">
-        <v>-7.444897019724968</v>
+        <v>-7.735728092646351</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>0.5999062029442754</v>
       </c>
       <c r="E90">
-        <v>-29.4425641656256</v>
+        <v>-31.14700479805459</v>
       </c>
       <c r="F90">
-        <v>-1.956093678339816</v>
+        <v>-2.760117848273252</v>
       </c>
       <c r="G90">
-        <v>-7.450301191633375</v>
+        <v>-7.377474479121498</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>0.4796880974920315</v>
       </c>
       <c r="E91">
-        <v>-30.75206525866064</v>
+        <v>-31.61720531121902</v>
       </c>
       <c r="F91">
-        <v>-1.652504480520422</v>
+        <v>-2.085006698665683</v>
       </c>
       <c r="G91">
-        <v>-7.280625943572929</v>
+        <v>-9.064314389394873</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>0.3649205391714148</v>
       </c>
       <c r="E92">
-        <v>-32.21678432678259</v>
+        <v>-35.30962791911927</v>
       </c>
       <c r="F92">
-        <v>-1.704760381391223</v>
+        <v>-1.676952916046647</v>
       </c>
       <c r="G92">
-        <v>-7.912966556401317</v>
+        <v>-8.225411035734762</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>0.2612846898311885</v>
       </c>
       <c r="E93">
-        <v>-33.98108232864497</v>
+        <v>-34.6333048545477</v>
       </c>
       <c r="F93">
-        <v>-1.878946993749695</v>
+        <v>-2.283232533053396</v>
       </c>
       <c r="G93">
-        <v>-8.041702003064572</v>
+        <v>-7.857317038753134</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>0.1745105120181698</v>
       </c>
       <c r="E94">
-        <v>-35.8766539992787</v>
+        <v>-36.35365175192864</v>
       </c>
       <c r="F94">
-        <v>-1.810861820178798</v>
+        <v>-2.212245588470493</v>
       </c>
       <c r="G94">
-        <v>-8.25300939027125</v>
+        <v>-8.678787262267916</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>0.107743672019755</v>
       </c>
       <c r="E95">
-        <v>-37.34379580099476</v>
+        <v>-39.47923394710377</v>
       </c>
       <c r="F95">
-        <v>-1.810029310938984</v>
+        <v>-2.370589674250424</v>
       </c>
       <c r="G95">
-        <v>-7.936046668850451</v>
+        <v>-9.501300914238602</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>0.06333502931674258</v>
       </c>
       <c r="E96">
-        <v>-39.50041362003765</v>
+        <v>-40.23003229520548</v>
       </c>
       <c r="F96">
-        <v>-1.569598985746039</v>
+        <v>-2.113257340570757</v>
       </c>
       <c r="G96">
-        <v>-9.180105417006118</v>
+        <v>-9.898781531506616</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>0.04153505306630444</v>
       </c>
       <c r="E97">
-        <v>-42.04480919683136</v>
+        <v>-42.826860808297</v>
       </c>
       <c r="F97">
-        <v>-1.705030429164536</v>
+        <v>-2.000306960096836</v>
       </c>
       <c r="G97">
-        <v>-9.294606924544501</v>
+        <v>-9.569904694603471</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>0.040496142557518</v>
       </c>
       <c r="E98">
-        <v>-43.46852293281385</v>
+        <v>-44.73342987805836</v>
       </c>
       <c r="F98">
-        <v>-1.709598875390975</v>
+        <v>-2.158055449714154</v>
       </c>
       <c r="G98">
-        <v>-10.05701515998928</v>
+        <v>-9.125912761730328</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>0.05781538685007287</v>
       </c>
       <c r="E99">
-        <v>-45.19206693284421</v>
+        <v>-46.05280757290413</v>
       </c>
       <c r="F99">
-        <v>-1.952845649753439</v>
+        <v>-2.355372565060997</v>
       </c>
       <c r="G99">
-        <v>-10.25387204744816</v>
+        <v>-9.69447955232935</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>0.08770879414763383</v>
       </c>
       <c r="E100">
-        <v>-47.17614989219486</v>
+        <v>-47.89414171034799</v>
       </c>
       <c r="F100">
-        <v>-1.856435281211215</v>
+        <v>-2.557052691518384</v>
       </c>
       <c r="G100">
-        <v>-10.75722127833166</v>
+        <v>-10.59801968948896</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>0.127773510667601</v>
       </c>
       <c r="E101">
-        <v>-49.16882902733057</v>
+        <v>-49.61968276741572</v>
       </c>
       <c r="F101">
-        <v>-1.840596896469689</v>
+        <v>-2.838952745630278</v>
       </c>
       <c r="G101">
-        <v>-10.83197078667737</v>
+        <v>-10.52295518387355</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>0.1684106530210888</v>
       </c>
       <c r="E102">
-        <v>-51.44910248974541</v>
+        <v>-52.27479500522297</v>
       </c>
       <c r="F102">
-        <v>-2.006537111333291</v>
+        <v>-3.199899759154315</v>
       </c>
       <c r="G102">
-        <v>-11.04142756492452</v>
+        <v>-11.84739073534937</v>
       </c>
     </row>
   </sheetData>
